--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/109.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/109.xlsx
@@ -426,13 +426,13 @@
         <v>-19.82993102457181</v>
       </c>
       <c r="E2">
-        <v>-10.93922389875852</v>
+        <v>-12.78875683839327</v>
       </c>
       <c r="F2">
-        <v>-3.266714217129318</v>
+        <v>-3.869823672085554</v>
       </c>
       <c r="G2">
-        <v>-7.770702341541402</v>
+        <v>-9.15000472447781</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.17478340424973</v>
       </c>
       <c r="E3">
-        <v>-11.46663262406185</v>
+        <v>-13.47410515166212</v>
       </c>
       <c r="F3">
-        <v>-3.091640423282448</v>
+        <v>-3.848468360441383</v>
       </c>
       <c r="G3">
-        <v>-8.179763280010368</v>
+        <v>-8.886018512630788</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.47146112451173</v>
       </c>
       <c r="E4">
-        <v>-10.54941285617826</v>
+        <v>-12.98854858313768</v>
       </c>
       <c r="F4">
-        <v>-3.147836867888366</v>
+        <v>-3.423366776672732</v>
       </c>
       <c r="G4">
-        <v>-6.821370302699997</v>
+        <v>-9.488123982585734</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-20.64227500334804</v>
       </c>
       <c r="E5">
-        <v>-12.89975879326929</v>
+        <v>-14.35499750105618</v>
       </c>
       <c r="F5">
-        <v>-3.198594252127503</v>
+        <v>-3.181062684414655</v>
       </c>
       <c r="G5">
-        <v>-6.965319443838586</v>
+        <v>-9.228242847207406</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.66823659650985</v>
       </c>
       <c r="E6">
-        <v>-13.71937636086556</v>
+        <v>-15.79296913745183</v>
       </c>
       <c r="F6">
-        <v>-3.449975594385458</v>
+        <v>-3.278100127080797</v>
       </c>
       <c r="G6">
-        <v>-6.534600916451709</v>
+        <v>-9.009001968869173</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.50245260119521</v>
       </c>
       <c r="E7">
-        <v>-13.15772331511623</v>
+        <v>-15.72721116638645</v>
       </c>
       <c r="F7">
-        <v>-2.458235087303625</v>
+        <v>-3.553543057287869</v>
       </c>
       <c r="G7">
-        <v>-7.155036877057601</v>
+        <v>-9.266718007464817</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.13776993476768</v>
       </c>
       <c r="E8">
-        <v>-13.88822504271556</v>
+        <v>-15.88811237635298</v>
       </c>
       <c r="F8">
-        <v>-3.114383250326308</v>
+        <v>-3.409063356728593</v>
       </c>
       <c r="G8">
-        <v>-8.131919275876822</v>
+        <v>-8.860358474155897</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-19.56568595763423</v>
       </c>
       <c r="E9">
-        <v>-15.1699779112686</v>
+        <v>-16.3513979097077</v>
       </c>
       <c r="F9">
-        <v>-2.959168736594154</v>
+        <v>-3.115653965922203</v>
       </c>
       <c r="G9">
-        <v>-5.061629958027162</v>
+        <v>-7.752150044339327</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.77838171076965</v>
       </c>
       <c r="E10">
-        <v>-17.59906495440501</v>
+        <v>-16.98526653045735</v>
       </c>
       <c r="F10">
-        <v>-3.422564917026822</v>
+        <v>-3.12577578721701</v>
       </c>
       <c r="G10">
-        <v>-5.206939733382392</v>
+        <v>-8.41832119157025</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.80208551704357</v>
       </c>
       <c r="E11">
-        <v>-16.50983110134005</v>
+        <v>-18.18707824735299</v>
       </c>
       <c r="F11">
-        <v>-2.74647629388395</v>
+        <v>-3.126193284388021</v>
       </c>
       <c r="G11">
-        <v>-5.730757422424654</v>
+        <v>-8.520779265465155</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.66755156689377</v>
       </c>
       <c r="E12">
-        <v>-16.64999642882547</v>
+        <v>-17.55910569976132</v>
       </c>
       <c r="F12">
-        <v>-3.184874831202338</v>
+        <v>-3.200069574471889</v>
       </c>
       <c r="G12">
-        <v>-5.897450011418037</v>
+        <v>-7.471481993519916</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.40321359771663</v>
       </c>
       <c r="E13">
-        <v>-17.00191320090955</v>
+        <v>-18.76573118452711</v>
       </c>
       <c r="F13">
-        <v>-2.96286656868025</v>
+        <v>-2.948387534846718</v>
       </c>
       <c r="G13">
-        <v>-4.947955755845207</v>
+        <v>-7.114181434557455</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.07279859841897</v>
       </c>
       <c r="E14">
-        <v>-18.13400453198309</v>
+        <v>-19.41678989260988</v>
       </c>
       <c r="F14">
-        <v>-3.093690632604376</v>
+        <v>-3.033147744235969</v>
       </c>
       <c r="G14">
-        <v>-4.487008637139244</v>
+        <v>-5.663500379248821</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.7335607103542</v>
       </c>
       <c r="E15">
-        <v>-17.66390817372083</v>
+        <v>-20.55026693672977</v>
       </c>
       <c r="F15">
-        <v>-2.791831894289431</v>
+        <v>-2.967874877997577</v>
       </c>
       <c r="G15">
-        <v>-3.676193134206484</v>
+        <v>-5.685452606719728</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.43371815832093</v>
       </c>
       <c r="E16">
-        <v>-18.21181277238288</v>
+        <v>-20.77131533846618</v>
       </c>
       <c r="F16">
-        <v>-2.509253407274644</v>
+        <v>-2.739438484429765</v>
       </c>
       <c r="G16">
-        <v>-2.341427520409892</v>
+        <v>-4.860626875064773</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.24276381675441</v>
       </c>
       <c r="E17">
-        <v>-19.96334047754363</v>
+        <v>-22.43661637004688</v>
       </c>
       <c r="F17">
-        <v>-1.558281001921589</v>
+        <v>-2.620130384139358</v>
       </c>
       <c r="G17">
-        <v>-2.350001833356604</v>
+        <v>-5.016090093588947</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.210075507031</v>
       </c>
       <c r="E18">
-        <v>-23.78595218469039</v>
+        <v>-22.86950678586211</v>
       </c>
       <c r="F18">
-        <v>-2.054251073734543</v>
+        <v>-2.56319420744274</v>
       </c>
       <c r="G18">
-        <v>-3.23551317529194</v>
+        <v>-4.656571469115175</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.362964848565861</v>
       </c>
       <c r="E19">
-        <v>-22.12306482975578</v>
+        <v>-22.80221366210813</v>
       </c>
       <c r="F19">
-        <v>-2.315996948936325</v>
+        <v>-2.674378508613892</v>
       </c>
       <c r="G19">
-        <v>-1.926281799239745</v>
+        <v>-4.804460159445497</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.733496790996788</v>
       </c>
       <c r="E20">
-        <v>-21.43777538664904</v>
+        <v>-23.40070131543585</v>
       </c>
       <c r="F20">
-        <v>-2.295502311023663</v>
+        <v>-2.180538997760939</v>
       </c>
       <c r="G20">
-        <v>-3.243974929690317</v>
+        <v>-5.00245064596715</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.326010766571485</v>
       </c>
       <c r="E21">
-        <v>-24.56177035168448</v>
+        <v>-25.206190316872</v>
       </c>
       <c r="F21">
-        <v>-1.875973154773644</v>
+        <v>-1.954965441937203</v>
       </c>
       <c r="G21">
-        <v>-2.601692679070774</v>
+        <v>-4.398017862498095</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.121726971676039</v>
       </c>
       <c r="E22">
-        <v>-23.38530450380977</v>
+        <v>-24.97544645228517</v>
       </c>
       <c r="F22">
-        <v>-1.96681523763425</v>
+        <v>-1.525480137872937</v>
       </c>
       <c r="G22">
-        <v>-2.339295529082601</v>
+        <v>-4.298797502140599</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.105949785434499</v>
       </c>
       <c r="E23">
-        <v>-24.5210457849335</v>
+        <v>-25.47985505810354</v>
       </c>
       <c r="F23">
-        <v>-1.424980119463093</v>
+        <v>-1.382562738235341</v>
       </c>
       <c r="G23">
-        <v>-1.715300732021993</v>
+        <v>-5.222108653043333</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.248052781762161</v>
       </c>
       <c r="E24">
-        <v>-25.93399760243677</v>
+        <v>-26.49037497596716</v>
       </c>
       <c r="F24">
-        <v>-0.6364638156774659</v>
+        <v>-1.353698276084793</v>
       </c>
       <c r="G24">
-        <v>-1.733654396491712</v>
+        <v>-4.020913620119715</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.504478076419953</v>
       </c>
       <c r="E25">
-        <v>-26.15752760792938</v>
+        <v>-26.02656866810156</v>
       </c>
       <c r="F25">
-        <v>-1.301460599296853</v>
+        <v>-1.33125366130594</v>
       </c>
       <c r="G25">
-        <v>-1.742265125439356</v>
+        <v>-4.954398077464629</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.838894054310833</v>
       </c>
       <c r="E26">
-        <v>-26.65380760290398</v>
+        <v>-26.54540046363436</v>
       </c>
       <c r="F26">
-        <v>-1.101339460291535</v>
+        <v>-1.235005652774666</v>
       </c>
       <c r="G26">
-        <v>-2.568861998957822</v>
+        <v>-4.357867566197815</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.213015175955588</v>
       </c>
       <c r="E27">
-        <v>-26.96386316126116</v>
+        <v>-27.81171123582125</v>
       </c>
       <c r="F27">
-        <v>-0.8023940901322348</v>
+        <v>-1.406133104314599</v>
       </c>
       <c r="G27">
-        <v>-3.104518198848518</v>
+        <v>-4.141129460287269</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.587954915062392</v>
       </c>
       <c r="E28">
-        <v>-25.10496533737854</v>
+        <v>-27.02979774281284</v>
       </c>
       <c r="F28">
-        <v>-0.5351934155830179</v>
+        <v>-1.434522911943343</v>
       </c>
       <c r="G28">
-        <v>-2.56269114207262</v>
+        <v>-5.018241948189473</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.938457371762272</v>
       </c>
       <c r="E29">
-        <v>-27.35721547051542</v>
+        <v>-26.60406684440373</v>
       </c>
       <c r="F29">
-        <v>-1.191479087594566</v>
+        <v>-1.146361228633688</v>
       </c>
       <c r="G29">
-        <v>-2.93553140179642</v>
+        <v>-4.859256309211514</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.249642272872951</v>
       </c>
       <c r="E30">
-        <v>-26.25819105664588</v>
+        <v>-26.64662544312782</v>
       </c>
       <c r="F30">
-        <v>-0.7187223555102624</v>
+        <v>-1.007907072562375</v>
       </c>
       <c r="G30">
-        <v>-2.357725336099723</v>
+        <v>-4.741963680755136</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.509838233385366</v>
       </c>
       <c r="E31">
-        <v>-25.35704737148952</v>
+        <v>-27.84156746495382</v>
       </c>
       <c r="F31">
-        <v>-1.060100017510564</v>
+        <v>-1.121034723660495</v>
       </c>
       <c r="G31">
-        <v>-2.744383812904441</v>
+        <v>-5.220526212275561</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.719126295862104</v>
       </c>
       <c r="E32">
-        <v>-25.28218716766872</v>
+        <v>-27.54177795717203</v>
       </c>
       <c r="F32">
-        <v>-0.4735918736738327</v>
+        <v>-1.049698208033611</v>
       </c>
       <c r="G32">
-        <v>-2.569212916784985</v>
+        <v>-5.002897569614952</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.886909131309954</v>
       </c>
       <c r="E33">
-        <v>-26.29447771886935</v>
+        <v>-26.9278165081601</v>
       </c>
       <c r="F33">
-        <v>-1.10004803551057</v>
+        <v>-0.9866809862330409</v>
       </c>
       <c r="G33">
-        <v>-2.306613823518916</v>
+        <v>-4.620234921276134</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.01965279719965</v>
       </c>
       <c r="E34">
-        <v>-23.78025989286275</v>
+        <v>-26.61512084945646</v>
       </c>
       <c r="F34">
-        <v>-0.3719909549856678</v>
+        <v>-0.9837750733840203</v>
       </c>
       <c r="G34">
-        <v>-2.245626953594462</v>
+        <v>-4.556725415650756</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.12872581023232</v>
       </c>
       <c r="E35">
-        <v>-24.56740377335002</v>
+        <v>-26.13944541121676</v>
       </c>
       <c r="F35">
-        <v>-0.4069430891793901</v>
+        <v>-1.011377103612703</v>
       </c>
       <c r="G35">
-        <v>-4.122643373995979</v>
+        <v>-5.596041392795092</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.22932852966035</v>
       </c>
       <c r="E36">
-        <v>-23.88428799776695</v>
+        <v>-26.07536750400822</v>
       </c>
       <c r="F36">
-        <v>-0.6289124184335456</v>
+        <v>-1.088551124327116</v>
       </c>
       <c r="G36">
-        <v>-3.698413515866072</v>
+        <v>-5.157149128471754</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.3287827558617</v>
       </c>
       <c r="E37">
-        <v>-25.54857917964394</v>
+        <v>-25.82847057263602</v>
       </c>
       <c r="F37">
-        <v>-0.9657879035996317</v>
+        <v>-1.144590179126502</v>
       </c>
       <c r="G37">
-        <v>-4.314274302536692</v>
+        <v>-5.594955533858211</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.43655114327899</v>
       </c>
       <c r="E38">
-        <v>-23.05173257993077</v>
+        <v>-24.78717061694226</v>
       </c>
       <c r="F38">
-        <v>-0.3301111842023332</v>
+        <v>-0.9176075703506041</v>
       </c>
       <c r="G38">
-        <v>-3.387470526090026</v>
+        <v>-5.282499624770717</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.56123573848904</v>
       </c>
       <c r="E39">
-        <v>-23.48518452652295</v>
+        <v>-24.1069485362501</v>
       </c>
       <c r="F39">
-        <v>-0.3051151978228581</v>
+        <v>-0.996724112624582</v>
       </c>
       <c r="G39">
-        <v>-3.027160681232368</v>
+        <v>-4.860765917977422</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.7003297971308</v>
       </c>
       <c r="E40">
-        <v>-23.23392214620736</v>
+        <v>-23.95736851130274</v>
       </c>
       <c r="F40">
-        <v>-0.7057012483056569</v>
+        <v>-0.7919351233044883</v>
       </c>
       <c r="G40">
-        <v>-2.865572953460541</v>
+        <v>-5.312129007347195</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.85277396853983</v>
       </c>
       <c r="E41">
-        <v>-20.8966680274725</v>
+        <v>-23.7468171123161</v>
       </c>
       <c r="F41">
-        <v>-0.4156889922181473</v>
+        <v>-0.9516766648929422</v>
       </c>
       <c r="G41">
-        <v>-2.316399796133001</v>
+        <v>-5.152014472340344</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.01585835248936</v>
       </c>
       <c r="E42">
-        <v>-21.23434727727647</v>
+        <v>-23.73596688859373</v>
       </c>
       <c r="F42">
-        <v>-0.5233759262146802</v>
+        <v>-1.143240768627342</v>
       </c>
       <c r="G42">
-        <v>-3.096215350636026</v>
+        <v>-5.070853137899571</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.17870584449387</v>
       </c>
       <c r="E43">
-        <v>-21.5668731236597</v>
+        <v>-24.41935890109126</v>
       </c>
       <c r="F43">
-        <v>-0.2227108653271688</v>
+        <v>-0.6277295097823479</v>
       </c>
       <c r="G43">
-        <v>-2.438456299620391</v>
+        <v>-4.985712527720595</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.33536988923766</v>
       </c>
       <c r="E44">
-        <v>-21.24429180619731</v>
+        <v>-21.49243859639563</v>
       </c>
       <c r="F44">
-        <v>-0.8348892866092539</v>
+        <v>-1.034353530264152</v>
       </c>
       <c r="G44">
-        <v>-3.997269703878239</v>
+        <v>-5.50043614816648</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.47986677854085</v>
       </c>
       <c r="E45">
-        <v>-19.99607228767107</v>
+        <v>-21.10694318954467</v>
       </c>
       <c r="F45">
-        <v>-0.2592849428955726</v>
+        <v>-0.7505672835760838</v>
       </c>
       <c r="G45">
-        <v>-3.052648571339217</v>
+        <v>-4.951726467214437</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.60197892977918</v>
       </c>
       <c r="E46">
-        <v>-19.99445562245033</v>
+        <v>-20.89532307069223</v>
       </c>
       <c r="F46">
-        <v>-0.1474685973960841</v>
+        <v>-0.8102370727019406</v>
       </c>
       <c r="G46">
-        <v>-3.4447330322828</v>
+        <v>-4.750197007511304</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.69919040184387</v>
       </c>
       <c r="E47">
-        <v>-19.97396427756562</v>
+        <v>-20.8525652191118</v>
       </c>
       <c r="F47">
-        <v>-0.3609214813820579</v>
+        <v>-0.4240008307378375</v>
       </c>
       <c r="G47">
-        <v>-2.940520393924102</v>
+        <v>-5.177465946446261</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.76940727934263</v>
       </c>
       <c r="E48">
-        <v>-18.17978287572663</v>
+        <v>-20.13948000254598</v>
       </c>
       <c r="F48">
-        <v>-0.3553092922280913</v>
+        <v>-0.9637095297860078</v>
       </c>
       <c r="G48">
-        <v>-2.013263072738556</v>
+        <v>-5.712056150673312</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.80685182752966</v>
       </c>
       <c r="E49">
-        <v>-17.35620742184765</v>
+        <v>-20.29451683867258</v>
       </c>
       <c r="F49">
-        <v>-0.241174346368167</v>
+        <v>-1.018742118190993</v>
       </c>
       <c r="G49">
-        <v>-2.75265686620708</v>
+        <v>-4.774903608870884</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.81224805004987</v>
       </c>
       <c r="E50">
-        <v>-17.61156354266618</v>
+        <v>-19.51075119979503</v>
       </c>
       <c r="F50">
-        <v>-1.057747454086613</v>
+        <v>-0.8581349326666136</v>
       </c>
       <c r="G50">
-        <v>-3.16501510803316</v>
+        <v>-5.34966728321699</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.78484029071839</v>
       </c>
       <c r="E51">
-        <v>-16.2397574399966</v>
+        <v>-18.37829759080087</v>
       </c>
       <c r="F51">
-        <v>-0.3021057390484875</v>
+        <v>-1.012304875103838</v>
       </c>
       <c r="G51">
-        <v>-2.491613729344468</v>
+        <v>-4.985345057165736</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.72180861238468</v>
       </c>
       <c r="E52">
-        <v>-16.21349229075211</v>
+        <v>-17.54103708847072</v>
       </c>
       <c r="F52">
-        <v>-0.3975974481410061</v>
+        <v>-1.216947243393636</v>
       </c>
       <c r="G52">
-        <v>-3.954126674410458</v>
+        <v>-5.485197707049214</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.62813048936048</v>
       </c>
       <c r="E53">
-        <v>-16.34470029665035</v>
+        <v>-17.0397304873476</v>
       </c>
       <c r="F53">
-        <v>-0.486452277602295</v>
+        <v>-0.836582469580576</v>
       </c>
       <c r="G53">
-        <v>-3.259157091533414</v>
+        <v>-5.826356045962188</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.50662717666115</v>
       </c>
       <c r="E54">
-        <v>-16.11948569882689</v>
+        <v>-17.5180596113558</v>
       </c>
       <c r="F54">
-        <v>-0.7117069119759534</v>
+        <v>-0.9699396810224629</v>
       </c>
       <c r="G54">
-        <v>-3.90024092466774</v>
+        <v>-6.388417157074112</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.35867723184029</v>
       </c>
       <c r="E55">
-        <v>-15.07477580220535</v>
+        <v>-16.70831411709624</v>
       </c>
       <c r="F55">
-        <v>-0.09733663054606086</v>
+        <v>-0.9263692123700145</v>
       </c>
       <c r="G55">
-        <v>-4.940470612380915</v>
+        <v>-5.837578795340318</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.19257685520772</v>
       </c>
       <c r="E56">
-        <v>-14.28752323834189</v>
+        <v>-16.18616295011582</v>
       </c>
       <c r="F56">
-        <v>-0.9484700546767053</v>
+        <v>-0.7940093552810983</v>
       </c>
       <c r="G56">
-        <v>-2.515747606325755</v>
+        <v>-5.700326887827673</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.01225807663111</v>
       </c>
       <c r="E57">
-        <v>-14.12277735394285</v>
+        <v>-15.38407057692923</v>
       </c>
       <c r="F57">
-        <v>-0.6784554160601785</v>
+        <v>-1.076687246384221</v>
       </c>
       <c r="G57">
-        <v>-3.141698935800072</v>
+        <v>-6.209886057232294</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.82077460139223</v>
       </c>
       <c r="E58">
-        <v>-14.3753756340907</v>
+        <v>-15.27588986136</v>
       </c>
       <c r="F58">
-        <v>0.009902985052960337</v>
+        <v>-0.8580860589898485</v>
       </c>
       <c r="G58">
-        <v>-3.694778536863953</v>
+        <v>-6.320438414970717</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.62626935940911</v>
       </c>
       <c r="E59">
-        <v>-12.79427704820862</v>
+        <v>-15.27851184781044</v>
       </c>
       <c r="F59">
-        <v>-0.5710625524916393</v>
+        <v>-0.7132344214667157</v>
       </c>
       <c r="G59">
-        <v>-3.941410868994117</v>
+        <v>-6.132184242880061</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.43037380017727</v>
       </c>
       <c r="E60">
-        <v>-10.9445810835096</v>
+        <v>-14.27408725596114</v>
       </c>
       <c r="F60">
-        <v>-0.758714276982617</v>
+        <v>-1.009028682025766</v>
       </c>
       <c r="G60">
-        <v>-4.327476758147305</v>
+        <v>-5.46791003824314</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.23422575966142</v>
       </c>
       <c r="E61">
-        <v>-12.46888807686148</v>
+        <v>-14.04193050748391</v>
       </c>
       <c r="F61">
-        <v>-0.2322785088295031</v>
+        <v>-1.026349844418304</v>
       </c>
       <c r="G61">
-        <v>-4.049817993223091</v>
+        <v>-5.712820886692883</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.04355823403539</v>
       </c>
       <c r="E62">
-        <v>-11.17982172278605</v>
+        <v>-13.53203791964225</v>
       </c>
       <c r="F62">
-        <v>-0.3920705808295278</v>
+        <v>-1.031282772301975</v>
       </c>
       <c r="G62">
-        <v>-4.469869942882437</v>
+        <v>-5.67862957236329</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.857199982514263</v>
       </c>
       <c r="E63">
-        <v>-11.88248239218622</v>
+        <v>-14.21509482506321</v>
       </c>
       <c r="F63">
-        <v>-0.957300451190548</v>
+        <v>-1.13735770333266</v>
       </c>
       <c r="G63">
-        <v>-4.311728493016992</v>
+        <v>-6.665072826699926</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.674784663729692</v>
       </c>
       <c r="E64">
-        <v>-11.63082150615796</v>
+        <v>-13.17481377602118</v>
       </c>
       <c r="F64">
-        <v>-0.7972399881520164</v>
+        <v>-1.083179161719961</v>
       </c>
       <c r="G64">
-        <v>-4.703975170691999</v>
+        <v>-6.434009990240954</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.500523889704031</v>
       </c>
       <c r="E65">
-        <v>-10.87654529001836</v>
+        <v>-12.79592088427341</v>
       </c>
       <c r="F65">
-        <v>-0.261245688537999</v>
+        <v>-1.527881574973653</v>
       </c>
       <c r="G65">
-        <v>-3.561330446175931</v>
+        <v>-6.685330054854727</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.332456370579921</v>
       </c>
       <c r="E66">
-        <v>-10.9225591144103</v>
+        <v>-12.58480795450982</v>
       </c>
       <c r="F66">
-        <v>-0.4649354343145778</v>
+        <v>-0.8231612609204185</v>
       </c>
       <c r="G66">
-        <v>-4.644772684813213</v>
+        <v>-6.393763688120034</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.170457903693585</v>
       </c>
       <c r="E67">
-        <v>-10.69602220217659</v>
+        <v>-12.92487371011583</v>
       </c>
       <c r="F67">
-        <v>-0.5154376813936525</v>
+        <v>-1.282686480479805</v>
       </c>
       <c r="G67">
-        <v>-4.05776992360842</v>
+        <v>-6.966911816242976</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.018822944927589</v>
       </c>
       <c r="E68">
-        <v>-11.28796168208922</v>
+        <v>-12.28196172677286</v>
       </c>
       <c r="F68">
-        <v>-1.25703359874991</v>
+        <v>-1.224034754891989</v>
       </c>
       <c r="G68">
-        <v>-4.122030923071214</v>
+        <v>-6.254207640912057</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.876007645250409</v>
       </c>
       <c r="E69">
-        <v>-11.72870900030776</v>
+        <v>-11.95885963479959</v>
       </c>
       <c r="F69">
-        <v>-0.7697497875227119</v>
+        <v>-1.091577150449542</v>
       </c>
       <c r="G69">
-        <v>-3.370388111107387</v>
+        <v>-6.47223023849184</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.742422904636237</v>
       </c>
       <c r="E70">
-        <v>-10.68187524937663</v>
+        <v>-11.70516093546787</v>
       </c>
       <c r="F70">
-        <v>-0.9073109635338062</v>
+        <v>-0.9511216587330665</v>
       </c>
       <c r="G70">
-        <v>-4.954775479656106</v>
+        <v>-7.047060123748731</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.623374136530781</v>
       </c>
       <c r="E71">
-        <v>-9.588497842594656</v>
+        <v>-12.74575444921644</v>
       </c>
       <c r="F71">
-        <v>-0.179910778359324</v>
+        <v>-1.462157248500735</v>
       </c>
       <c r="G71">
-        <v>-4.289998072097216</v>
+        <v>-7.353116748308814</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.51839029277515</v>
       </c>
       <c r="E72">
-        <v>-8.92929240977209</v>
+        <v>-12.43205346928309</v>
       </c>
       <c r="F72">
-        <v>-0.501466436778036</v>
+        <v>-0.8061457660995138</v>
       </c>
       <c r="G72">
-        <v>-4.656574779660715</v>
+        <v>-7.398345421466336</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.428533565332446</v>
       </c>
       <c r="E73">
-        <v>-11.36632239631795</v>
+        <v>-13.19290502968182</v>
       </c>
       <c r="F73">
-        <v>-1.069386844463349</v>
+        <v>-1.284242154462262</v>
       </c>
       <c r="G73">
-        <v>-4.347399621202639</v>
+        <v>-6.433715351687959</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.359709171024985</v>
       </c>
       <c r="E74">
-        <v>-12.0778271754551</v>
+        <v>-11.95973363028307</v>
       </c>
       <c r="F74">
-        <v>-1.160829493690984</v>
+        <v>-1.469089026927361</v>
       </c>
       <c r="G74">
-        <v>-4.570795234192659</v>
+        <v>-6.466754596169885</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.31161259699072</v>
       </c>
       <c r="E75">
-        <v>-13.209538114712</v>
+        <v>-12.47640534371421</v>
       </c>
       <c r="F75">
-        <v>-0.9803862223391674</v>
+        <v>-1.499956481457879</v>
       </c>
       <c r="G75">
-        <v>-4.558827612068193</v>
+        <v>-6.12523540779313</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.284496580437491</v>
       </c>
       <c r="E76">
-        <v>-11.71755536882687</v>
+        <v>-13.18407903384087</v>
       </c>
       <c r="F76">
-        <v>-0.8922520725183141</v>
+        <v>-1.639468462702566</v>
       </c>
       <c r="G76">
-        <v>-4.702038501551526</v>
+        <v>-7.049870776911573</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.283114600252279</v>
       </c>
       <c r="E77">
-        <v>-10.88623169592077</v>
+        <v>-13.45128164266346</v>
       </c>
       <c r="F77">
-        <v>-1.39227948787018</v>
+        <v>-2.096762060478811</v>
       </c>
       <c r="G77">
-        <v>-3.364313260042824</v>
+        <v>-6.017785031225006</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.304920672816399</v>
       </c>
       <c r="E78">
-        <v>-11.68501375460775</v>
+        <v>-13.65176171545704</v>
       </c>
       <c r="F78">
-        <v>-1.947165534472442</v>
+        <v>-1.936616275597791</v>
       </c>
       <c r="G78">
-        <v>-4.690915068539574</v>
+        <v>-6.212382208568905</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.346079684152256</v>
       </c>
       <c r="E79">
-        <v>-12.33561961528975</v>
+        <v>-13.32416284879415</v>
       </c>
       <c r="F79">
-        <v>-0.9906803440537569</v>
+        <v>-1.913639848946341</v>
       </c>
       <c r="G79">
-        <v>-4.472726943682829</v>
+        <v>-6.2891703123523</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.407362108223424</v>
       </c>
       <c r="E80">
-        <v>-11.75957055067003</v>
+        <v>-13.81975904419359</v>
       </c>
       <c r="F80">
-        <v>-1.357134344071605</v>
+        <v>-1.94464067062871</v>
       </c>
       <c r="G80">
-        <v>-3.967342372203228</v>
+        <v>-5.843574193311937</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.482774910374143</v>
       </c>
       <c r="E81">
-        <v>-13.29494513449666</v>
+        <v>-14.86543803425277</v>
       </c>
       <c r="F81">
-        <v>-1.979801553407937</v>
+        <v>-2.006227301924644</v>
       </c>
       <c r="G81">
-        <v>-4.491554016164663</v>
+        <v>-5.820277884352087</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.565478114794342</v>
       </c>
       <c r="E82">
-        <v>-14.12520461601096</v>
+        <v>-15.43448154958262</v>
       </c>
       <c r="F82">
-        <v>-1.741167957111664</v>
+        <v>-1.932457042868335</v>
       </c>
       <c r="G82">
-        <v>-4.298820675959374</v>
+        <v>-6.812051117006948</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.65578157824169</v>
       </c>
       <c r="E83">
-        <v>-14.75962118211554</v>
+        <v>-16.64108439197837</v>
       </c>
       <c r="F83">
-        <v>-2.277457983888481</v>
+        <v>-2.204718213881253</v>
       </c>
       <c r="G83">
-        <v>-3.419668892004978</v>
+        <v>-5.674382142436405</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.749040944202886</v>
       </c>
       <c r="E84">
-        <v>-15.33838733113985</v>
+        <v>-17.12457597635531</v>
       </c>
       <c r="F84">
-        <v>-1.754797914357327</v>
+        <v>-2.202077378601129</v>
       </c>
       <c r="G84">
-        <v>-4.270187767590217</v>
+        <v>-5.909288522266471</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.841194118901729</v>
       </c>
       <c r="E85">
-        <v>-16.72567175796765</v>
+        <v>-17.72642828587073</v>
       </c>
       <c r="F85">
-        <v>-1.51517773248432</v>
+        <v>-2.350230060224417</v>
       </c>
       <c r="G85">
-        <v>-3.04977170726559</v>
+        <v>-6.056607798764039</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.938394222211162</v>
       </c>
       <c r="E86">
-        <v>-17.65901742179255</v>
+        <v>-18.87538818262285</v>
       </c>
       <c r="F86">
-        <v>-2.194418293594845</v>
+        <v>-2.580917128025635</v>
       </c>
       <c r="G86">
-        <v>-4.821628648612158</v>
+        <v>-6.338255771063074</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.041798117038311</v>
       </c>
       <c r="E87">
-        <v>-18.35911044643037</v>
+        <v>-19.742753980156</v>
       </c>
       <c r="F87">
-        <v>-2.479495965063878</v>
+        <v>-2.501837862284783</v>
       </c>
       <c r="G87">
-        <v>-3.810402650368538</v>
+        <v>-6.038856653582466</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.151547110346977</v>
       </c>
       <c r="E88">
-        <v>-18.77538136263746</v>
+        <v>-19.48438189564837</v>
       </c>
       <c r="F88">
-        <v>-2.608814885417117</v>
+        <v>-3.073788277384716</v>
       </c>
       <c r="G88">
-        <v>-2.528413753559007</v>
+        <v>-6.143764531176431</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.278750539997056</v>
       </c>
       <c r="E89">
-        <v>-20.67292971217553</v>
+        <v>-22.44866663938129</v>
       </c>
       <c r="F89">
-        <v>-2.398545417360102</v>
+        <v>-3.301464229676757</v>
       </c>
       <c r="G89">
-        <v>-3.587391060661074</v>
+        <v>-6.471114584645106</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.427124236903317</v>
       </c>
       <c r="E90">
-        <v>-22.33872887589708</v>
+        <v>-23.03833282534207</v>
       </c>
       <c r="F90">
-        <v>-2.791763968162401</v>
+        <v>-3.185004884884577</v>
       </c>
       <c r="G90">
-        <v>-5.037211374129497</v>
+        <v>-6.468529048578935</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.597110132074018</v>
       </c>
       <c r="E91">
-        <v>-25.41796893231471</v>
+        <v>-24.8039033284006</v>
       </c>
       <c r="F91">
-        <v>-2.998658667420412</v>
+        <v>-3.166428745876798</v>
       </c>
       <c r="G91">
-        <v>-5.370623036480578</v>
+        <v>-6.850430271443719</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.800556146015607</v>
       </c>
       <c r="E92">
-        <v>-25.87398626488712</v>
+        <v>-26.28845031996514</v>
       </c>
       <c r="F92">
-        <v>-3.053068323538492</v>
+        <v>-3.543248935573279</v>
       </c>
       <c r="G92">
-        <v>-6.009621225925162</v>
+        <v>-7.253853350859306</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.03948826218306</v>
       </c>
       <c r="E93">
-        <v>-27.63849257655385</v>
+        <v>-28.66040613502077</v>
       </c>
       <c r="F93">
-        <v>-2.752676623893904</v>
+        <v>-3.37240064384809</v>
       </c>
       <c r="G93">
-        <v>-5.452999341134262</v>
+        <v>-7.255975410549979</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.31099738718142</v>
       </c>
       <c r="E94">
-        <v>-30.20609205416287</v>
+        <v>-29.08909412695689</v>
       </c>
       <c r="F94">
-        <v>-2.784056009479352</v>
+        <v>-3.549472459870512</v>
       </c>
       <c r="G94">
-        <v>-5.484065500474784</v>
+        <v>-7.478069979143065</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.62181838929168</v>
       </c>
       <c r="E95">
-        <v>-31.03168267897525</v>
+        <v>-31.64269156293419</v>
       </c>
       <c r="F95">
-        <v>-2.508311553537661</v>
+        <v>-3.733241626344569</v>
       </c>
       <c r="G95">
-        <v>-6.358754669042241</v>
+        <v>-7.057769738568274</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.96710506538125</v>
       </c>
       <c r="E96">
-        <v>-32.79964648054684</v>
+        <v>-33.98220991867288</v>
       </c>
       <c r="F96">
-        <v>-3.453497812582162</v>
+        <v>-3.873413816409287</v>
       </c>
       <c r="G96">
-        <v>-5.404241626431876</v>
+        <v>-8.093838070538585</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.33102273746099</v>
       </c>
       <c r="E97">
-        <v>-33.75918710226912</v>
+        <v>-35.310651354245</v>
       </c>
       <c r="F97">
-        <v>-3.372887723880936</v>
+        <v>-3.739364918186062</v>
       </c>
       <c r="G97">
-        <v>-5.821886809484172</v>
+        <v>-7.677053629326499</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.71519686264935</v>
       </c>
       <c r="E98">
-        <v>-37.81066335728953</v>
+        <v>-37.95657305405368</v>
       </c>
       <c r="F98">
-        <v>-3.434172001074849</v>
+        <v>-3.719424458065873</v>
       </c>
       <c r="G98">
-        <v>-5.913906733293754</v>
+        <v>-8.654515373615093</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.09188919892133</v>
       </c>
       <c r="E99">
-        <v>-39.62374660963655</v>
+        <v>-40.31791186179833</v>
       </c>
       <c r="F99">
-        <v>-3.69944754977996</v>
+        <v>-3.911131040993554</v>
       </c>
       <c r="G99">
-        <v>-6.789976399351088</v>
+        <v>-8.851072393918241</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.45594911495803</v>
       </c>
       <c r="E100">
-        <v>-41.70272827029194</v>
+        <v>-42.06231627734501</v>
       </c>
       <c r="F100">
-        <v>-3.647598377303933</v>
+        <v>-4.145082704729204</v>
       </c>
       <c r="G100">
-        <v>-6.540652593697497</v>
+        <v>-8.393485478934638</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.77539905872995</v>
       </c>
       <c r="E101">
-        <v>-45.58701552918617</v>
+        <v>-43.46860670958299</v>
       </c>
       <c r="F101">
-        <v>-3.742924412915892</v>
+        <v>-3.840101849673108</v>
       </c>
       <c r="G101">
-        <v>-6.157043129334448</v>
+        <v>-9.166554141628627</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.0720715067152</v>
       </c>
       <c r="E102">
-        <v>-46.63093520709337</v>
+        <v>-46.45943736794888</v>
       </c>
       <c r="F102">
-        <v>-3.664383585986859</v>
+        <v>-4.104023846042044</v>
       </c>
       <c r="G102">
-        <v>-6.072607665355337</v>
+        <v>-8.140920649198099</v>
       </c>
     </row>
   </sheetData>
